--- a/reports/jobs_2026-09-29.xlsx
+++ b/reports/jobs_2026-09-29.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Silicon Power &amp; Performance Engineer (System Level Test &amp; Characterization)</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,11 +538,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -550,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/bengaluru/silicon-power-and-performance-engineer-system-level-test-and-characterization/33099/96899126992</t>
+          <t>https://www.sirion.ai/jobs/integration-support-engineer/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -567,106 +563,98 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Infrastructure Transformation Engineer – IT</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>DevOps / SRE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sirionlabs.com/careers/</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>https://careers.arm.com/job/bengaluru/design-engineer/33099/100290447600</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.arm.com/</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Ixigo</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Backend Engineer (Java / .NET)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, in</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -679,7 +667,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -687,12 +679,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -709,7 +701,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,7 +726,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -756,7 +748,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -781,7 +773,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -803,7 +795,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -828,7 +820,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -863,11 +855,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -875,7 +863,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -897,7 +885,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -918,7 +906,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -940,7 +928,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -953,7 +941,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -961,7 +953,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -983,12 +975,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -996,11 +988,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1008,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1030,12 +1018,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1051,7 +1039,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1073,12 +1061,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1094,7 +1082,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1111,12 +1099,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1129,7 +1117,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1137,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1154,12 +1146,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1172,11 +1164,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1184,12 +1172,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1206,12 +1194,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1227,7 +1215,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1244,12 +1232,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1262,7 +1250,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1270,12 +1262,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1292,7 +1284,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>AI Engineer, FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1307,7 +1299,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru, India; Delhi, India; Mumbai, India; Pune, India</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1317,7 +1309,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8015848002</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1334,17 +1326,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer, FDE (Forward Deployed Engineer)</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1354,7 +1346,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India; Delhi, India; Mumbai, India; Pune, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1364,12 +1356,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8015848002</t>
+          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer-</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1381,17 +1373,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1401,7 +1393,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1411,12 +1403,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1428,17 +1420,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1446,7 +1438,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1454,12 +1450,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1471,12 +1467,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SME - Data Science &amp; AI expert</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1489,7 +1485,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Gurgaon/SME---Data-Science---AI-expert_SR-46203</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1514,12 +1514,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1532,7 +1532,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1540,12 +1544,12 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1557,17 +1561,17 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1583,12 +1587,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1600,17 +1604,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1618,7 +1622,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1626,12 +1634,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1643,12 +1651,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1661,7 +1669,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -1669,12 +1681,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1686,17 +1698,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1706,7 +1718,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1716,12 +1728,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1733,17 +1745,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1753,7 +1765,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1763,12 +1775,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1780,12 +1792,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1800,7 +1812,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1810,12 +1822,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1827,17 +1839,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1847,7 +1859,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1857,12 +1869,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1874,17 +1886,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1894,7 +1906,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1904,12 +1916,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1921,17 +1933,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1947,12 +1959,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1964,12 +1976,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>SME - Data Science &amp; AI expert</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1990,12 +2002,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://fractal.ai/en-US/Careers/job/Gurgaon/SME---Data-Science---AI-expert_SR-46203</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2007,12 +2019,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2025,11 +2037,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2037,12 +2045,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2054,12 +2062,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2072,11 +2080,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2084,12 +2088,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2101,17 +2105,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2127,12 +2131,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2144,12 +2148,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2162,11 +2166,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2191,17 +2191,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2209,7 +2209,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2217,12 +2221,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2234,12 +2238,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2252,7 +2256,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2260,12 +2268,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2277,17 +2285,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2297,7 +2305,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2307,12 +2315,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2324,17 +2332,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Backend Engineer (Java / .NET)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2344,7 +2352,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2354,12 +2362,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2371,17 +2379,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2391,7 +2399,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2401,12 +2409,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2418,17 +2426,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2438,7 +2446,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2448,12 +2456,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2465,12 +2473,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2483,11 +2491,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2495,12 +2499,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2512,12 +2516,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2538,12 +2542,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2555,17 +2559,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2575,7 +2579,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2585,12 +2589,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2602,12 +2606,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2622,7 +2626,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2632,12 +2636,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2649,17 +2653,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2667,11 +2671,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2696,17 +2696,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2714,7 +2714,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2722,12 +2726,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2739,17 +2743,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2757,11 +2761,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2786,17 +2786,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2804,11 +2804,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2816,12 +2812,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2833,12 +2829,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2853,7 +2849,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2863,12 +2859,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2880,17 +2876,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2900,7 +2896,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2910,12 +2906,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2927,12 +2923,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2947,7 +2943,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2957,12 +2953,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2974,17 +2970,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2994,7 +2990,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3004,12 +3000,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3021,17 +3017,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3039,7 +3035,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3064,17 +3064,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3082,11 +3082,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3094,12 +3090,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3111,17 +3107,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3141,12 +3137,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3158,17 +3154,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3176,7 +3172,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3184,12 +3184,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3201,17 +3201,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3248,12 +3248,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Developer (Vapasi) - Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3263,14 +3263,10 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1–5 years</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3278,12 +3274,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3295,17 +3291,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3315,7 +3311,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3325,12 +3321,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3342,52 +3338,608 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer (CPD) - Winter Intern</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer - IAM</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Rubrik India</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer - Winter Intern</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/rubrik</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Scaler</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.scaler.com/careers/</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>ShareChat</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Sound Designer - AI</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>https://sharechat.com/careers</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>QA / SDET</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Sprinklr</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Internship and Early Careers</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Developer (Vapasi) - Intern</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>1–5 years</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I76"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -3452,6 +4004,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3463,7 +4027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3511,19 +4075,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>INDmoney</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.indmoney.com/careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://exotel.com/careers/", waiting until "networkidle"
+  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -3591,35 +4155,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ather Energy</t>
+          <t>Capillary Technologies</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.atherenergy.com/careers</t>
+          <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3628,18 +4172,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3648,38 +4192,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Darwinbox</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://darwinbox.com/careers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -3688,18 +4212,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3708,18 +4232,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3728,18 +4252,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3748,58 +4272,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PharmEasy</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://pharmeasy.in/careers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pharmeasy.in/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Pocket FM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://pocketfm.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3808,18 +4292,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -3828,18 +4312,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -3848,18 +4332,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -3868,18 +4352,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
